--- a/artfynd/A 21670-2022 artfynd.xlsx
+++ b/artfynd/A 21670-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 21670-2022 artfynd.xlsx
+++ b/artfynd/A 21670-2022 artfynd.xlsx
@@ -7924,7 +7924,7 @@
         <v>120019238</v>
       </c>
       <c r="B62" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>

--- a/artfynd/A 21670-2022 artfynd.xlsx
+++ b/artfynd/A 21670-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY62"/>
+  <dimension ref="A1:AY63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8038,6 +8038,121 @@
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>121603496</v>
+      </c>
+      <c r="B63" t="n">
+        <v>57984</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>102125</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Tallbit</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Pinicola enucleator</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Garphytteklint, Nrk</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>496498</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6574921</v>
+      </c>
+      <c r="S63" t="n">
+        <v>25</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Tysslinge</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2024-12-13</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2024-12-13</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Satt i toppen av en spenslig rönn, alldelens nära Garphytteklints högsta punkt. Jag tror de var där för att äta rönnbär.</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Josefina Jansson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Josefina Jansson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21670-2022 artfynd.xlsx
+++ b/artfynd/A 21670-2022 artfynd.xlsx
@@ -8043,7 +8043,7 @@
         <v>121603496</v>
       </c>
       <c r="B63" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>

--- a/artfynd/A 21670-2022 artfynd.xlsx
+++ b/artfynd/A 21670-2022 artfynd.xlsx
@@ -8043,7 +8043,7 @@
         <v>121603496</v>
       </c>
       <c r="B63" t="n">
-        <v>57985</v>
+        <v>57993</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>

--- a/artfynd/A 21670-2022 artfynd.xlsx
+++ b/artfynd/A 21670-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY63"/>
+  <dimension ref="A1:AY64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8153,6 +8153,115 @@
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>126020943</v>
+      </c>
+      <c r="B64" t="n">
+        <v>57933</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>103012</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Grönsångare</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Phylloscopus sibilatrix</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Garphytteklint, Nrk</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>496477</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6575000</v>
+      </c>
+      <c r="S64" t="n">
+        <v>50</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Tysslinge</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Michael Andersson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21670-2022 artfynd.xlsx
+++ b/artfynd/A 21670-2022 artfynd.xlsx
@@ -8158,7 +8158,7 @@
         <v>126020943</v>
       </c>
       <c r="B64" t="n">
-        <v>57933</v>
+        <v>57934</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 21670-2022 artfynd.xlsx
+++ b/artfynd/A 21670-2022 artfynd.xlsx
@@ -8158,7 +8158,7 @@
         <v>126020943</v>
       </c>
       <c r="B64" t="n">
-        <v>57934</v>
+        <v>57938</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 21670-2022 artfynd.xlsx
+++ b/artfynd/A 21670-2022 artfynd.xlsx
@@ -8158,7 +8158,7 @@
         <v>126020943</v>
       </c>
       <c r="B64" t="n">
-        <v>57938</v>
+        <v>57939</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>

--- a/artfynd/A 21670-2022 artfynd.xlsx
+++ b/artfynd/A 21670-2022 artfynd.xlsx
@@ -8267,7 +8267,7 @@
         <v>129140235</v>
       </c>
       <c r="B65" t="n">
-        <v>86866</v>
+        <v>86869</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8376,7 +8376,7 @@
         <v>129140233</v>
       </c>
       <c r="B66" t="n">
-        <v>86825</v>
+        <v>86828</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8485,7 +8485,7 @@
         <v>129140234</v>
       </c>
       <c r="B67" t="n">
-        <v>88710</v>
+        <v>88713</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>

--- a/artfynd/A 21670-2022 artfynd.xlsx
+++ b/artfynd/A 21670-2022 artfynd.xlsx
@@ -8267,7 +8267,7 @@
         <v>129140235</v>
       </c>
       <c r="B65" t="n">
-        <v>86869</v>
+        <v>86872</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8376,7 +8376,7 @@
         <v>129140233</v>
       </c>
       <c r="B66" t="n">
-        <v>86828</v>
+        <v>86831</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8485,7 +8485,7 @@
         <v>129140234</v>
       </c>
       <c r="B67" t="n">
-        <v>88713</v>
+        <v>88716</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>

--- a/artfynd/A 21670-2022 artfynd.xlsx
+++ b/artfynd/A 21670-2022 artfynd.xlsx
@@ -8267,7 +8267,7 @@
         <v>129140235</v>
       </c>
       <c r="B65" t="n">
-        <v>86872</v>
+        <v>86876</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8376,7 +8376,7 @@
         <v>129140233</v>
       </c>
       <c r="B66" t="n">
-        <v>86831</v>
+        <v>86835</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8485,7 +8485,7 @@
         <v>129140234</v>
       </c>
       <c r="B67" t="n">
-        <v>88716</v>
+        <v>88720</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>

--- a/artfynd/A 21670-2022 artfynd.xlsx
+++ b/artfynd/A 21670-2022 artfynd.xlsx
@@ -8267,7 +8267,7 @@
         <v>129140235</v>
       </c>
       <c r="B65" t="n">
-        <v>86876</v>
+        <v>86883</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8376,7 +8376,7 @@
         <v>129140233</v>
       </c>
       <c r="B66" t="n">
-        <v>86835</v>
+        <v>86842</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8485,7 +8485,7 @@
         <v>129140234</v>
       </c>
       <c r="B67" t="n">
-        <v>88720</v>
+        <v>88727</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>

--- a/artfynd/A 21670-2022 artfynd.xlsx
+++ b/artfynd/A 21670-2022 artfynd.xlsx
@@ -8267,7 +8267,7 @@
         <v>129140235</v>
       </c>
       <c r="B65" t="n">
-        <v>86883</v>
+        <v>86885</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8376,7 +8376,7 @@
         <v>129140233</v>
       </c>
       <c r="B66" t="n">
-        <v>86842</v>
+        <v>86844</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8485,7 +8485,7 @@
         <v>129140234</v>
       </c>
       <c r="B67" t="n">
-        <v>88727</v>
+        <v>88729</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>

--- a/artfynd/A 21670-2022 artfynd.xlsx
+++ b/artfynd/A 21670-2022 artfynd.xlsx
@@ -8267,7 +8267,7 @@
         <v>129140235</v>
       </c>
       <c r="B65" t="n">
-        <v>86885</v>
+        <v>86886</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8376,7 +8376,7 @@
         <v>129140233</v>
       </c>
       <c r="B66" t="n">
-        <v>86844</v>
+        <v>86845</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8485,7 +8485,7 @@
         <v>129140234</v>
       </c>
       <c r="B67" t="n">
-        <v>88729</v>
+        <v>88730</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>

--- a/artfynd/A 21670-2022 artfynd.xlsx
+++ b/artfynd/A 21670-2022 artfynd.xlsx
@@ -8267,7 +8267,7 @@
         <v>129140235</v>
       </c>
       <c r="B65" t="n">
-        <v>86886</v>
+        <v>86889</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8376,7 +8376,7 @@
         <v>129140233</v>
       </c>
       <c r="B66" t="n">
-        <v>86845</v>
+        <v>86848</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8485,7 +8485,7 @@
         <v>129140234</v>
       </c>
       <c r="B67" t="n">
-        <v>88730</v>
+        <v>88733</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>

--- a/artfynd/A 21670-2022 artfynd.xlsx
+++ b/artfynd/A 21670-2022 artfynd.xlsx
@@ -8267,7 +8267,7 @@
         <v>129140235</v>
       </c>
       <c r="B65" t="n">
-        <v>86889</v>
+        <v>86891</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8376,7 +8376,7 @@
         <v>129140233</v>
       </c>
       <c r="B66" t="n">
-        <v>86848</v>
+        <v>86850</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8485,7 +8485,7 @@
         <v>129140234</v>
       </c>
       <c r="B67" t="n">
-        <v>88733</v>
+        <v>88735</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>

--- a/artfynd/A 21670-2022 artfynd.xlsx
+++ b/artfynd/A 21670-2022 artfynd.xlsx
@@ -8267,7 +8267,7 @@
         <v>129140235</v>
       </c>
       <c r="B65" t="n">
-        <v>86891</v>
+        <v>86895</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8376,7 +8376,7 @@
         <v>129140233</v>
       </c>
       <c r="B66" t="n">
-        <v>86850</v>
+        <v>86854</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8485,7 +8485,7 @@
         <v>129140234</v>
       </c>
       <c r="B67" t="n">
-        <v>88735</v>
+        <v>88739</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>

--- a/artfynd/A 21670-2022 artfynd.xlsx
+++ b/artfynd/A 21670-2022 artfynd.xlsx
@@ -8267,7 +8267,7 @@
         <v>129140235</v>
       </c>
       <c r="B65" t="n">
-        <v>86895</v>
+        <v>86896</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8376,7 +8376,7 @@
         <v>129140233</v>
       </c>
       <c r="B66" t="n">
-        <v>86854</v>
+        <v>86855</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8485,7 +8485,7 @@
         <v>129140234</v>
       </c>
       <c r="B67" t="n">
-        <v>88739</v>
+        <v>88740</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>

--- a/artfynd/A 21670-2022 artfynd.xlsx
+++ b/artfynd/A 21670-2022 artfynd.xlsx
@@ -8267,7 +8267,7 @@
         <v>129140235</v>
       </c>
       <c r="B65" t="n">
-        <v>86896</v>
+        <v>86924</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8376,7 +8376,7 @@
         <v>129140233</v>
       </c>
       <c r="B66" t="n">
-        <v>86855</v>
+        <v>86883</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8485,7 +8485,7 @@
         <v>129140234</v>
       </c>
       <c r="B67" t="n">
-        <v>88740</v>
+        <v>88768</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>

--- a/artfynd/A 21670-2022 artfynd.xlsx
+++ b/artfynd/A 21670-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY236"/>
+  <dimension ref="A1:AZ236"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293166</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293231</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,6 +1035,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293358</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1129,6 +1149,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129140233</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1245,6 +1270,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293538</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1361,6 +1391,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293413</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1468,6 +1503,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293494</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1577,6 +1617,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96131562</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1693,6 +1738,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293351</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1794,6 +1844,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101863772</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1895,6 +1950,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101915356</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2001,6 +2061,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95450584</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2107,6 +2172,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95450705</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2213,6 +2283,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95450767</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2314,6 +2389,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91940451</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2422,6 +2502,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104653930</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2531,6 +2616,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96130123</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2652,6 +2742,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293182</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2759,6 +2854,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96131565</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2868,6 +2968,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129140235</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2989,6 +3094,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293110</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3095,6 +3205,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101915229</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3211,6 +3326,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293141</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3327,6 +3447,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293532</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3436,6 +3561,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96130126</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3557,6 +3687,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293750</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3669,6 +3804,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95450521</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3781,6 +3921,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95450686</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3883,6 +4028,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93777886</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3995,6 +4145,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95292991</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4097,6 +4252,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95292995</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4209,6 +4369,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95292989</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4326,6 +4491,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293020</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4433,6 +4603,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93777882</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4532,6 +4707,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94852857</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4644,6 +4824,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95292992</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4754,6 +4939,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96133451</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4881,6 +5071,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293321</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4993,6 +5188,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95292999</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5114,6 +5314,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293120</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5216,6 +5421,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293405</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5332,6 +5542,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293422</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5439,6 +5654,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293505</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5560,6 +5780,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293014</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5681,6 +5906,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293127</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5802,6 +6032,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293134</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5918,6 +6153,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293233</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6034,6 +6274,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293411</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6141,6 +6386,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293486</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6257,6 +6507,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293506</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6373,6 +6628,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293537</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6482,6 +6742,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96130116</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6588,6 +6853,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101915142</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6695,6 +6965,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293399</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6802,6 +7077,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293454</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6904,6 +7184,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293457</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7005,6 +7290,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75789395</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7121,6 +7411,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293359</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7242,6 +7537,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293529</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7363,6 +7663,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293530</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7464,6 +7769,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101915313</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7576,6 +7886,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293136</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7683,6 +7998,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293161</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7790,6 +8110,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293175</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7906,6 +8231,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293186</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8022,6 +8352,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293188</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8138,6 +8473,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293190</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8245,6 +8585,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293232</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8361,6 +8706,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293323</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8468,6 +8818,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293329</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8584,6 +8939,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293335</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8691,6 +9051,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293387</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8798,6 +9163,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293392</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8900,6 +9270,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293410</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9011,6 +9386,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293423</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9127,6 +9507,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293438</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9234,6 +9619,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293474</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9341,6 +9731,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293493</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9443,6 +9838,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293512</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9559,6 +9959,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293533</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9668,6 +10073,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96130109</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9777,6 +10187,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96131560</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9878,6 +10293,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101863436</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9994,6 +10414,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293193</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10101,6 +10526,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293304</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10208,6 +10638,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293309</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10310,6 +10745,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293315</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10426,6 +10866,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293192</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10528,6 +10973,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293515</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10635,6 +11085,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96130121</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10736,6 +11191,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129140234</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10852,6 +11312,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293194</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10959,6 +11424,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293308</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11061,6 +11531,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293313</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11177,6 +11652,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293350</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11293,6 +11773,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293459</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11400,6 +11885,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293503</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11509,6 +11999,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96130102</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11630,6 +12125,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293338</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11731,6 +12231,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101863579</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11832,6 +12337,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75789399</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11944,6 +12454,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293012</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -12065,6 +12580,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293132</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -12186,6 +12706,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293135</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12293,6 +12818,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293173</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12400,6 +12930,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293306</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12507,6 +13042,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293370</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12609,6 +13149,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293487</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12716,6 +13261,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293504</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12817,6 +13367,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95450760</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12926,6 +13481,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96130118</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -13035,6 +13595,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96131566</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -13148,6 +13713,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72658440</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -13284,6 +13854,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293223</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13420,6 +13995,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293356</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13556,6 +14136,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293468</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -13692,6 +14277,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293748</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13810,6 +14400,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103746084</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13918,6 +14513,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91567460</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -14026,6 +14626,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91567628</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -14134,6 +14739,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91568537</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -14235,6 +14845,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91938078</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -14371,6 +14986,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293225</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -14477,6 +15097,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95450598</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -14583,6 +15208,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95450624</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -14689,6 +15319,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95450695</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -14797,6 +15432,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91568052</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -14898,6 +15538,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91940772</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -15027,6 +15672,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95292983</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -15163,6 +15813,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293236</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -15294,6 +15949,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293319</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -15430,6 +16090,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293337</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -15536,6 +16201,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95450422</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -15642,6 +16312,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95450640</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -15748,6 +16423,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95450658</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -15869,6 +16549,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293139</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -15985,6 +16670,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293343</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -16101,6 +16791,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293465</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -16217,6 +16912,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293467</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -16333,6 +17033,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293476</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -16449,6 +17154,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293479</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -16570,6 +17280,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293482</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -16679,6 +17394,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96130100</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -16788,6 +17508,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96130106</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -16897,6 +17622,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96131570</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -17006,6 +17736,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96131571</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -17107,6 +17842,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101915210</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -17223,6 +17963,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293361</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -17324,6 +18069,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101863547</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -17440,6 +18190,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293156</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -17541,6 +18296,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101915145</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -17653,6 +18413,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293017</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -17774,6 +18539,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293107</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -17895,6 +18665,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293121</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -18002,6 +18777,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293152</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -18109,6 +18889,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293159</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -18216,6 +19001,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293171</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -18332,6 +19122,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293185</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -18448,6 +19243,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293373</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -18555,6 +19355,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293388</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -18671,6 +19476,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293395</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -18773,6 +19583,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293409</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -18889,6 +19704,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293424</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -18996,6 +19816,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293485</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -19098,6 +19923,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293514</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -19207,6 +20037,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96131567</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -19308,6 +20143,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101863390</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -19409,6 +20249,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101863477</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -19510,6 +20355,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75789390</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -19641,6 +20491,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293317</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -19752,6 +20607,11 @@
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112678862</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -19858,6 +20718,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96134019</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -19979,6 +20844,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293013</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -20093,6 +20963,11 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120019238</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -20204,6 +21079,11 @@
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95450653</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -20319,6 +21199,11 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91567274</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -20430,6 +21315,11 @@
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293183</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -20541,6 +21431,11 @@
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101661161</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -20646,6 +21541,11 @@
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95450781</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -20751,6 +21651,11 @@
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101863459</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -20854,6 +21759,11 @@
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91941864</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -20964,6 +21874,11 @@
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121603496</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -21072,6 +21987,11 @@
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91941698</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -21177,6 +22097,11 @@
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95269384</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -21286,6 +22211,11 @@
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126020943</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -21391,6 +22321,11 @@
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95269369</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -21496,6 +22431,11 @@
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95269401</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -21605,6 +22545,11 @@
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97718191</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -21714,6 +22659,11 @@
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101908676</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -21819,6 +22769,11 @@
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101915187</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -21933,6 +22888,11 @@
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101661255</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -22044,6 +23004,11 @@
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101661159</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -22158,6 +23123,11 @@
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101661254</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -22265,6 +23235,11 @@
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101908702</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -22377,6 +23352,11 @@
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293130</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -22483,6 +23463,11 @@
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96130114</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -22582,6 +23567,11 @@
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94853301</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -22694,6 +23684,11 @@
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293124</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -22801,6 +23796,11 @@
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293167</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -22903,6 +23903,11 @@
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293347</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -23010,6 +24015,11 @@
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293377</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -23117,6 +24127,11 @@
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293502</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -23250,6 +24265,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101804407</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -23376,6 +24396,11 @@
       <c r="AY205" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101804425</t>
         </is>
       </c>
     </row>
@@ -23485,6 +24510,11 @@
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101908583</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -23588,6 +24618,11 @@
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102058277</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -23708,6 +24743,11 @@
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103746453</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -23807,6 +24847,11 @@
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94852649</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -23919,6 +24964,11 @@
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293015</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -24031,6 +25081,11 @@
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293131</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -24138,6 +25193,11 @@
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293154</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -24245,6 +25305,11 @@
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293172</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -24352,6 +25417,11 @@
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293369</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -24459,6 +25529,11 @@
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293382</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -24566,6 +25641,11 @@
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293389</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -24673,6 +25753,11 @@
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293398</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -24775,6 +25860,11 @@
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
+      <c r="AZ218" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293404</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -24877,6 +25967,11 @@
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293421</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -24984,6 +26079,11 @@
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293490</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -25086,6 +26186,11 @@
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293517</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -25193,6 +26298,11 @@
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293519</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -25295,6 +26405,11 @@
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95269373</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -25402,6 +26517,11 @@
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293363</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -25509,6 +26629,11 @@
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293501</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -25620,6 +26745,11 @@
         </is>
       </c>
       <c r="AY226" t="inlineStr"/>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293525</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -25722,6 +26852,11 @@
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95450632</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -25824,6 +26959,11 @@
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101908715</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -25926,6 +27066,11 @@
         </is>
       </c>
       <c r="AY229" t="inlineStr"/>
+      <c r="AZ229" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101908730</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -26047,6 +27192,11 @@
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
+      <c r="AZ230" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293460</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -26148,6 +27298,11 @@
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
+      <c r="AZ231" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101863493</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -26254,6 +27409,11 @@
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
+      <c r="AZ232" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101863514</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -26355,6 +27515,11 @@
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
+      <c r="AZ233" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101863530</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -26471,6 +27636,11 @@
         </is>
       </c>
       <c r="AY234" t="inlineStr"/>
+      <c r="AZ234" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293191</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -26587,6 +27757,11 @@
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
+      <c r="AZ235" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95293483</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -26696,8 +27871,250 @@
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
+      <c r="AZ236" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96131557</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ233" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ236" r:id="rId235"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>